--- a/data/trans_orig/IP22D3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Provincia-trans_orig.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>40907</t>
+          <t>40870</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>46866</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>38614</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>49072</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>82183</t>
+          <t>82292</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>94239</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1522</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4285</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>56,36%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -1402,74 +1402,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7946</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6080</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3317</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7602</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6180</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3739</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7763</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>79,61%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>48,17%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8701</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -1477,27 +1477,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1971,64 +1971,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>351</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>363</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>714</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -2540,74 +2540,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4789</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8039</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>59,58%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5471</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3727</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5909</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>63,08%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5807</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6170</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>94,12%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>68,4%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>7554</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>4689</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8505</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>55,13%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>13</t>
@@ -2615,27 +2615,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2766,82 +2766,82 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>42,66%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,82 +2996,82 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>595</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>64,53%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>63,93%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,27 +3184,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>495</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,47 +3565,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3020</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>48,58%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>86,3%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1790</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>55,64%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>64,25%</t>
         </is>
       </c>
     </row>
@@ -3678,74 +3678,74 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>51,42%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2867</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1427</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>89,11%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>44,36%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>91,8%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>44,54%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>4070</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>49,81%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>3977</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>60,48%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -4247,74 +4247,74 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>7810</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>3963</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>10663</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>61,35%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>9949</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>7180</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>89,03%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>64,25%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>10339</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>7719</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>11526</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>66,97%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>8615</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>4689</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>11914</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>63,32%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>23</t>
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21864</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -4360,82 +4360,82 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5272,72 +5272,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>13022</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>7296</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>15,15%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -5385,72 +5385,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>40483</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>34183</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>44487</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>83,47%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>70,48%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>44630</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>40870</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>46866</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>84,85%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>38614</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>49034</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>80123</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>82292</t>
+          <t>73751</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>94198</t>
+          <t>84883</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -5498,82 +5498,82 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5583,12 +5583,12 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5611,82 +5611,82 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5724,57 +5724,57 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
